--- a/wnn_medcost/docs/proposals/위너넷_문서전산화_업무기술_웹앱구분.xlsx
+++ b/wnn_medcost/docs/proposals/위너넷_문서전산화_업무기술_웹앱구분.xlsx
@@ -3,13 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13935" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23925" windowHeight="7425" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="① 업무별 종합" sheetId="1" r:id="rId1"/>
@@ -19,6 +14,7 @@
     <sheet name="⑤ 앱(App) 구현 업무" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:N17"/>
 </workbook>
 </file>
 
